--- a/data/trans_orig/Q21A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q21A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según número de veces que utilizó un servicios de urgencias en el último año</t>
+          <t>Número medio de veces que la población utilizó un servicios de urgencias en el último año (tasa de respuesta: 96,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,47 +716,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,58</t>
+          <t>1,18; 1,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,47</t>
+          <t>1,19; 1,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,25; 1,65</t>
+          <t>1,25; 1,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,81</t>
+          <t>1,34; 2,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,16</t>
+          <t>1,48; 2,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,11</t>
+          <t>1,45; 2,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,48</t>
+          <t>1,67; 2,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,29</t>
+          <t>1,49; 2,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,74</t>
+          <t>1,36; 1,82</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,93</t>
+          <t>1,51; 1,95</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,37</t>
+          <t>1,52; 2,34</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,53</t>
+          <t>1,18; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,11</t>
+          <t>1,45; 2,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,78</t>
+          <t>1,37; 1,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,55</t>
+          <t>1,46; 2,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,77</t>
+          <t>1,39; 1,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,22</t>
+          <t>1,65; 2,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,25</t>
+          <t>1,75; 3,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,57</t>
+          <t>1,74; 2,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 1,6</t>
+          <t>1,34; 1,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,06</t>
+          <t>1,64; 2,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,46</t>
+          <t>1,66; 2,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,36</t>
+          <t>1,71; 2,35</t>
         </is>
       </c>
     </row>
@@ -1001,57 +1001,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,99</t>
+          <t>1,39; 2,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,89</t>
+          <t>1,45; 2,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,31</t>
+          <t>1,36; 2,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,38</t>
+          <t>1,57; 2,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,87</t>
+          <t>1,86; 2,88</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,31</t>
+          <t>1,5; 2,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,91</t>
+          <t>1,83; 2,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,89</t>
+          <t>1,4; 1,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,32</t>
+          <t>1,71; 2,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,25</t>
+          <t>1,52; 2,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,3</t>
+          <t>1,67; 2,35</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,45</t>
+          <t>1,22; 2,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,28</t>
+          <t>1,48; 2,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,35</t>
+          <t>1,54; 2,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,44</t>
+          <t>1,51; 2,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,22</t>
+          <t>1,5; 2,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,49</t>
+          <t>1,7; 2,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,04</t>
+          <t>1,56; 2,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,32</t>
+          <t>1,7; 3,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,07</t>
+          <t>1,45; 2,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,19</t>
+          <t>1,7; 2,23</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,05</t>
+          <t>1,61; 2,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,6</t>
+          <t>1,68; 2,5</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,1; 1,37</t>
+          <t>1,1; 1,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,53</t>
+          <t>1,51; 3,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,72</t>
+          <t>1,31; 1,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,85</t>
+          <t>1,43; 1,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,37</t>
+          <t>1,41; 2,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,9</t>
+          <t>1,43; 1,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,27</t>
+          <t>1,55; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,23</t>
+          <t>1,7; 2,2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 1,89</t>
+          <t>1,32; 1,84</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,56</t>
+          <t>1,54; 2,62</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 1,91</t>
+          <t>1,47; 1,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,0</t>
+          <t>1,6; 1,98</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,7</t>
+          <t>1,31; 1,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,22</t>
+          <t>1,39; 2,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,05</t>
+          <t>1,3; 2,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,97</t>
+          <t>1,41; 1,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 2,24</t>
+          <t>1,64; 2,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,58</t>
+          <t>1,64; 2,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,74</t>
+          <t>1,51; 2,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 14,13</t>
+          <t>1,63; 13,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,99</t>
+          <t>1,54; 1,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,24</t>
+          <t>1,63; 2,3</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,28</t>
+          <t>1,48; 2,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,29</t>
+          <t>1,59; 13,28</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,1</t>
+          <t>1,47; 2,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,97</t>
+          <t>1,61; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,9</t>
+          <t>1,42; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 6,65</t>
+          <t>1,47; 7,47</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,08</t>
+          <t>1,6; 2,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,13</t>
+          <t>1,64; 2,14</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,19</t>
+          <t>1,6; 2,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,41</t>
+          <t>1,52; 2,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,0</t>
+          <t>1,61; 2,02</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,73; 2,58</t>
+          <t>1,71; 2,59</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,02</t>
+          <t>1,59; 2,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,27</t>
+          <t>1,58; 3,26</t>
         </is>
       </c>
     </row>
@@ -1696,47 +1696,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,48</t>
+          <t>1,29; 1,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,57; 1,97</t>
+          <t>1,58; 1,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,83</t>
+          <t>1,5; 1,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,13</t>
+          <t>1,6; 2,12</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,86</t>
+          <t>1,63; 1,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 2,05</t>
+          <t>1,78; 2,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,12</t>
+          <t>1,76; 2,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,29</t>
+          <t>1,89; 9,53</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,67</t>
+          <t>1,52; 1,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,9</t>
+          <t>1,68; 1,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,74</t>
+          <t>1,82; 7,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q21A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q21A-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,78</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,83</t>
+          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,55</t>
+          <t>1,17; 1,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,45</t>
+          <t>1,18; 1,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,88</t>
+          <t>1,4; 3,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,18</t>
+          <t>1,47; 2,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,16</t>
+          <t>1,44; 2,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,49</t>
+          <t>1,67; 2,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 2,22</t>
+          <t>1,52; 2,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,82</t>
+          <t>1,38; 1,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 1,95</t>
+          <t>1,52; 1,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,34</t>
+          <t>1,55; 2,38</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,86</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,96</t>
+          <t>2,08</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 1,52</t>
+          <t>1,17; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,12</t>
+          <t>1,46; 2,12</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,76</t>
+          <t>1,37; 1,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,56</t>
+          <t>1,5; 2,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 1,77</t>
+          <t>1,39; 1,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,2</t>
+          <t>1,67; 2,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,11</t>
+          <t>1,76; 3,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,62</t>
+          <t>1,8; 3,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,6</t>
+          <t>1,34; 1,59</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,05</t>
+          <t>1,63; 2,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,47</t>
+          <t>1,68; 2,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,35</t>
+          <t>1,78; 2,65</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,2</t>
+          <t>2,13</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,88</t>
         </is>
       </c>
     </row>
@@ -1001,57 +1001,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,0</t>
+          <t>1,39; 2,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,95</t>
+          <t>1,4; 2,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,22</t>
+          <t>1,34; 2,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 2,41</t>
+          <t>1,58; 2,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,88</t>
+          <t>1,84; 2,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,26</t>
+          <t>1,49; 2,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,93</t>
+          <t>1,8; 2,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 1,86</t>
+          <t>1,42; 1,93</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,37</t>
+          <t>1,71; 2,34</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,3</t>
+          <t>1,53; 2,25</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,35</t>
+          <t>1,65; 2,34</t>
         </is>
       </c>
     </row>
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>1,75</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,76</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,72</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1,65</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,91</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>1,77</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,76</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2,12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1,65</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,95</t>
+          <t>1,94</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 2,27</t>
+          <t>1,22; 2,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,29</t>
+          <t>1,48; 2,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,3</t>
+          <t>1,55; 2,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,38</t>
+          <t>1,48; 2,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 2,24</t>
+          <t>1,51; 2,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,45</t>
+          <t>1,72; 2,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,0</t>
+          <t>1,53; 2,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,41</t>
+          <t>1,71; 3,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,05</t>
+          <t>1,43; 2,06</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,23</t>
+          <t>1,68; 2,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,61; 2,08</t>
+          <t>1,6; 2,03</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,5</t>
+          <t>1,67; 2,45</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,88</t>
+          <t>1,91</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 3,68</t>
+          <t>1,52; 3,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,71</t>
+          <t>1,3; 1,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,89</t>
+          <t>1,41; 1,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,41; 2,31</t>
+          <t>1,43; 2,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,43; 1,93</t>
+          <t>1,41; 1,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 2,28</t>
+          <t>1,57; 2,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,2</t>
+          <t>1,71; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 2,62</t>
+          <t>1,55; 2,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 1,88</t>
+          <t>1,49; 1,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,98</t>
+          <t>1,63; 1,97</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,61</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>1,81</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,28</t>
+          <t>1,74</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 1,67</t>
+          <t>1,31; 1,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,2</t>
+          <t>1,37; 2,22</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,0</t>
+          <t>1,3; 1,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 1,98</t>
+          <t>1,43; 2,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,28</t>
+          <t>1,63; 2,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,61</t>
+          <t>1,61; 2,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,51; 2,93</t>
+          <t>1,53; 2,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,82</t>
+          <t>1,61; 2,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,95</t>
+          <t>1,55; 1,99</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,3</t>
+          <t>1,61; 2,28</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,48; 2,33</t>
+          <t>1,49; 2,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 13,28</t>
+          <t>1,59; 2,01</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,53</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,76</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,07</t>
+          <t>1,46; 2,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 4,02</t>
+          <t>1,61; 4,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 1,86</t>
+          <t>1,42; 1,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,47</t>
+          <t>1,48; 6,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,12</t>
+          <t>1,61; 2,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,16</t>
+          <t>1,6; 2,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,5</t>
+          <t>1,52; 2,35</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,59</t>
+          <t>1,72; 2,65</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,01</t>
+          <t>1,58; 2,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,26</t>
+          <t>1,6; 3,58</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>1,8</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,58</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,48</t>
+          <t>1,9</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,29; 1,49</t>
+          <t>1,28; 1,47</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 1,96</t>
+          <t>1,58; 1,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,8</t>
+          <t>1,5; 1,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,12</t>
+          <t>1,63; 2,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,63; 1,87</t>
+          <t>1,64; 1,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,05</t>
+          <t>1,77; 2,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 2,09</t>
+          <t>1,75; 2,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,89; 9,53</t>
+          <t>1,84; 2,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,7</t>
+          <t>1,51; 1,68</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 1,94</t>
+          <t>1,73; 1,95</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 1,9</t>
+          <t>1,67; 1,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 7,26</t>
+          <t>1,77; 2,09</t>
         </is>
       </c>
     </row>
